--- a/Dev_GNC/TableData/EquipmentDataTable.xlsx
+++ b/Dev_GNC/TableData/EquipmentDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E540DAC2-9132-4062-AC90-49E834C45A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D3E33D-531B-4973-BF31-9B1A45420210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39180" yWindow="2460" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipmentData" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
     <t>idAlias</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>slot</t>
   </si>
   <si>
@@ -254,6 +251,10 @@
   </si>
   <si>
     <t>Textures/Icon/Equipment/equip_weapon_sniper</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>nameAlias</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -551,44 +552,44 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -596,37 +597,37 @@
         <v>10001</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="E2" s="1">
         <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J2" s="1">
         <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -634,40 +635,40 @@
         <v>10002</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1">
         <v>100</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H3" s="1">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J3" s="1">
         <v>3</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -675,34 +676,34 @@
         <v>10003</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H4" s="1">
         <v>5</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J4" s="1">
         <v>2</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -710,40 +711,40 @@
         <v>10004</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1">
         <v>100</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H5" s="1">
         <v>3</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J5" s="1">
         <v>2</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -751,28 +752,28 @@
         <v>30001</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="E6" s="1">
         <v>100</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
@@ -783,22 +784,22 @@
         <v>30002</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1">
         <v>100</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H7" s="1">
         <v>2</v>
@@ -809,28 +810,28 @@
         <v>30003</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1">
         <v>100</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8" s="1">
         <v>3</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J8" s="1">
         <v>5</v>
@@ -841,26 +842,26 @@
         <v>50101</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="E9" s="1">
         <v>50</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -868,26 +869,26 @@
         <v>50102</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1">
         <v>50</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -895,26 +896,26 @@
         <v>50103</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" s="1">
         <v>50</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -922,26 +923,26 @@
         <v>50104</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" s="1">
         <v>50</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -949,26 +950,26 @@
         <v>50105</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" s="1">
         <v>50</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -976,26 +977,26 @@
         <v>50201</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E14" s="1">
         <v>50</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -1003,26 +1004,26 @@
         <v>50301</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
@@ -1030,22 +1031,22 @@
         <v>60101</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E16" s="1">
         <v>100</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
@@ -1056,22 +1057,22 @@
         <v>60102</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="D17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" s="1">
         <v>100</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
